--- a/gelenler.xlsx
+++ b/gelenler.xlsx
@@ -21592,7 +21592,7 @@
       </c>
       <c r="G244" s="3" t="inlineStr">
         <is>
-          <t>Sənəd icradadır</t>
+          <t>İcra edilib</t>
         </is>
       </c>
       <c r="H244" s="3" t="inlineStr">
